--- a/data/trans_bre/IP07B_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP07B_R2-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,44 +619,30 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,9</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-4,29</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,82</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-25,74%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-0,98%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>-0.8974457455903497</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.04049905088394021</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-4.28907686939147</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.821726709657823</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.2573898245495845</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.009782885038034586</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -655,254 +650,150 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-5,7; 5,29</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-5,11; 6,31</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-12,43; -1,09</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,35</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 508,76</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.700360118916174</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.113544581134017</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-12.43298210063621</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>5.288356336302869</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.308287473578924</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-1.085845366143669</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>9.354703521065206</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="n">
+        <v>5.087594089482868</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-2,13</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,06</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-35,48%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-42,04%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-12,2%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-42,56%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-4,64; 1,93</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-7,27; 2,3</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,89; 2,2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-4,95; 3,28</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 292,44</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-89,9; 106,81</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-1.038546263432169</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-2.129431866398268</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.1669510910722623</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.056942732153359</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.3548417890155289</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.4203853502349963</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.1220082908237942</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.4256202513495437</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,38</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,77</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,71</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>20,95%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>365,63%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-4.643209873791564</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-7.27475916437016</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.89203569352164</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-4.948400491623901</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.8990183807936494</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,19; 3,5</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,23; 4,61</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-0,23; 9,35</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,82</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.928768383782849</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.302217741908393</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.196590639795944</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.278121471031341</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>2.924355631331799</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.06813605768224</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,44 +801,30 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2,91</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,42</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,05</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,03%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-41,41%</t>
+      <c r="C10" s="5" t="n">
+        <v>0.05130008991122634</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.3765596716630293</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>3.76705495991708</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.713529831467147</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.04729791335744589</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.2095467322316874</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>3.656317364721446</v>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -955,152 +832,238 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,91; 8,71</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,41; 4,55</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,45; 2,35</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-6,78; 3,09</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.192957839863072</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.232813643586788</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.2292653191434143</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3.495124785380208</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4.609878395634373</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9.34883586661137</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.815389116349471</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2.906440228949545</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.4182080553045496</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.05011709303870743</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.0512739383644</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.1310394233404922</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.07026329795868033</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.4141240407176811</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.9085616718391407</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.413097642191175</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.450105587066296</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-6.780067896776155</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>8.710262669330977</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.549906283984564</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.353605183803633</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3.086667523998864</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,28</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>15,23%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-12,29%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-8,41%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-8,61%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,57; 2,44</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,83; 1,94</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,87; 1,49</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,27; 1,68</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-62,28; 238,28</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-58,81; 83,02</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-71,16; 184,35</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 282,38</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.2839642999543139</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.4479617256320623</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.1431068327300781</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.1253895486138853</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.1522837378403357</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.1228768053861659</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.08412222187683181</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.08607058836357369</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.5667290888949</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.8266818738968</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.866977084903392</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.265197276176746</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.6227929288818084</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.5880776911383191</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.7115841398245444</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.439829687839148</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.937722399442161</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.49285524139396</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.682598887999257</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>2.382792856701301</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.8302012717837844</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1.843535158006919</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>2.823813403698435</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1071,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
